--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.05526013123386</v>
+        <v>2.771479771325502</v>
       </c>
       <c r="D2" t="n">
-        <v>15.28220705625256</v>
+        <v>2.483358646641041</v>
       </c>
       <c r="E2" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F2" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.51442466414362</v>
+        <v>5.771094007923338</v>
       </c>
       <c r="D3" t="n">
-        <v>35.58210530048067</v>
+        <v>5.782092111328109</v>
       </c>
       <c r="E3" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F3" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.05561716692023</v>
+        <v>6.346537789624537</v>
       </c>
       <c r="D4" t="n">
-        <v>39.16178509945967</v>
+        <v>6.363790078662197</v>
       </c>
       <c r="E4" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F4" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.53343641055697</v>
+        <v>3.824183416715508</v>
       </c>
       <c r="D5" t="n">
-        <v>23.61511099503867</v>
+        <v>3.837455536693784</v>
       </c>
       <c r="E5" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F5" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.72196098190582</v>
+        <v>5.479818659559696</v>
       </c>
       <c r="D6" t="n">
-        <v>31.74176363757769</v>
+        <v>5.158036591106375</v>
       </c>
       <c r="E6" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F6" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.30431999918623</v>
+        <v>5.411951999867763</v>
       </c>
       <c r="D7" t="n">
-        <v>33.20578701742209</v>
+        <v>5.39594039033109</v>
       </c>
       <c r="E7" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F7" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.573375848657209</v>
+        <v>1.555673575406797</v>
       </c>
       <c r="D8" t="n">
-        <v>9.467740308478563</v>
+        <v>1.538507800127767</v>
       </c>
       <c r="E8" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F8" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.703633217510056</v>
+        <v>1.576840397845384</v>
       </c>
       <c r="D9" t="n">
-        <v>9.678235073745039</v>
+        <v>1.572713199483569</v>
       </c>
       <c r="E9" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F9" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.44074038096404</v>
+        <v>3.646620311906657</v>
       </c>
       <c r="D10" t="n">
-        <v>22.33382929176109</v>
+        <v>3.629247259911177</v>
       </c>
       <c r="E10" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F10" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.5884312251201</v>
+        <v>5.295620074082017</v>
       </c>
       <c r="D11" t="n">
-        <v>32.60146762344208</v>
+        <v>5.297738488809339</v>
       </c>
       <c r="E11" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F11" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.87920083698615</v>
+        <v>3.880370136010249</v>
       </c>
       <c r="D12" t="n">
-        <v>24.09530715985513</v>
+        <v>3.915487413476459</v>
       </c>
       <c r="E12" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F12" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.16056833512337</v>
+        <v>6.038592354457548</v>
       </c>
       <c r="D13" t="n">
-        <v>37.08945634189823</v>
+        <v>6.027036655558463</v>
       </c>
       <c r="E13" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F13" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.35926394498571</v>
+        <v>4.770880391060177</v>
       </c>
       <c r="D14" t="n">
-        <v>29.6194257206026</v>
+        <v>4.813156679597922</v>
       </c>
       <c r="E14" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F14" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.23683366272346</v>
+        <v>1.825985470192562</v>
       </c>
       <c r="D15" t="n">
-        <v>10.99452096884663</v>
+        <v>1.786609657437578</v>
       </c>
       <c r="E15" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F15" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>19.94198509661708</v>
+        <v>3.240572578200275</v>
       </c>
       <c r="D16" t="n">
-        <v>19.67878974294611</v>
+        <v>3.197803333228743</v>
       </c>
       <c r="E16" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F16" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.95345559177887</v>
+        <v>4.217436533664066</v>
       </c>
       <c r="D17" t="n">
-        <v>26.086135228393</v>
+        <v>4.238996974613863</v>
       </c>
       <c r="E17" t="n">
-        <v>9.478779100302443</v>
+        <v>1.540301603799147</v>
       </c>
       <c r="F17" t="n">
-        <v>9.541136950436092</v>
+        <v>1.550434754445865</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
